--- a/public/template/Template_Upload_Data_Mahasiswa.xlsx
+++ b/public/template/Template_Upload_Data_Mahasiswa.xlsx
@@ -1,162 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PERSONAL\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B642EA-7E6D-46B2-883D-88C1E6B267BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>nim</t>
-  </si>
-  <si>
-    <t>nik</t>
-  </si>
-  <si>
-    <t>nidn</t>
-  </si>
-  <si>
-    <t>gelar_depan</t>
-  </si>
-  <si>
-    <t>gelar_belakang</t>
-  </si>
-  <si>
-    <t>jabatan</t>
-  </si>
-  <si>
-    <t>photo</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>Alfanda Handy Fabian</t>
-  </si>
-  <si>
-    <t>alfanda.20225001@student.atmi.ac.id</t>
-  </si>
-  <si>
-    <t>pmatmi</t>
-  </si>
-  <si>
-    <t>20225001</t>
-  </si>
-  <si>
-    <t>Mahasiswa</t>
-  </si>
-  <si>
-    <t>Catatan: Sheet ini HANYA untuk data Mahasiswa (role = Mahasiswa). Data Dosen tidak lagi diisi lewat file ini — kolom nik/nidn/gelar dikosongkan untuk mahasiswa. Baris berwarna abu-abu miring adalah contoh, hapus/ganti dengan data asli.</t>
-  </si>
-  <si>
-    <t>nama</t>
-  </si>
-  <si>
-    <t>alamat</t>
-  </si>
-  <si>
-    <t>PT. Dharma Electrindo Manufactur</t>
-  </si>
-  <si>
-    <t>Jl Jababeka XII Blok W no 5A Kawasan Industri Jababeka I Cikarang Utara Bekasi 17530</t>
-  </si>
-  <si>
-    <t>Catatan: daftar perusahaan tempat mahasiswa magang. Baris berwarna abu-abu miring adalah contoh, hapus/ganti dengan data asli.</t>
-  </si>
-  <si>
-    <t>nim_mahasiswa</t>
-  </si>
-  <si>
-    <t>nama_perusahaan</t>
-  </si>
-  <si>
-    <t>tanggal_presentasi</t>
-  </si>
-  <si>
-    <t>jam_presentasi</t>
-  </si>
-  <si>
-    <t>jam_presentasi_selesai</t>
-  </si>
-  <si>
-    <t>lokasi</t>
-  </si>
-  <si>
-    <t>Catatan: 'nim_mahasiswa' harus cocok dengan NIM di Sheet1, dan 'nama_perusahaan' harus cocok persis dengan 'nama' di Sheet2. Tanggal/jam presentasi &amp; lokasi boleh dikosongkan, diisi belakangan lewat sistem. Baris berwarna abu-abu miring adalah contoh, hapus/ganti dengan data asli.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="9">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="16"/>
     </font>
     <font>
-      <i/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <i/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
-        <bgColor rgb="FF2F5496"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -164,34 +103,159 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -479,188 +543,854 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="11" width="22" customWidth="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PANDUAN UPLOAD DATA PESERTA MAGANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sheet ini HANYA panduan. Sheet ini TIDAK ikut diproses sistem saat upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>File ini berisi 4 sheet: Petunjuk (sheet ini), Sheet1, Sheet2, Sheet3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Yang perlu Anda isi HANYA Sheet1, Sheet2, dan Sheet3. Sheet Petunjuk boleh dibiarkan saja, tidak perlu dihapus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>JANGAN mengubah judul kolom (baris paling atas / baris ke-1) di Sheet1, Sheet2, Sheet3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>JANGAN menambahkan baris catatan, keterangan, atau baris kosong di antara data pada Sheet1, Sheet2, Sheet3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Mulai isi data dari baris ke-2 pada masing-masing sheet, satu baris = satu data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Jangan ada baris kosong yang diselipkan di tengah data (langsung isi baris demi baris tanpa jeda).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Setelah semua data terisi, simpan file (tetap format .xlsx), lalu upload lewat menu Import Peserta Magang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>SHEET1 — Data Mahasiswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Kolom</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Wajib?</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Nama lengkap mahasiswa.</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Email mahasiswa, harus pakai domain @student.atmi.ac.id, dan harus unik (belum pernah dipakai).</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Password awal untuk login. Bebas isi apa saja, mahasiswa bisa ganti sendiri nanti.</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>nim</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>NIM mahasiswa, harus unik. Kolom ini sudah diformat sebagai Teks, jadi aman diketik langsung.</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>nik / nidn / gelar_depan / gelar_belakang / jabatan</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Kosongkan</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Kolom ini khusus untuk data Dosen. Untuk Mahasiswa, biarkan KOSONG (kolomnya tetap ada, jangan dihapus).</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Kosongkan</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Biarkan kosong. Foto diatur lewat sistem, bukan lewat file ini.</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Ketik persis: Mahasiswa (sudah tersedia pilihan dropdown di Sheet1 supaya tidak salah ketik).</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Contoh pengisian 1 baris data (baris ini hanya contoh, TIDAK ada di Sheet1 yang sebenarnya):</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>nim</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>nik</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>nidn</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>gelar_depan</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>gelar_belakang</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>jabatan</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Alfanda Handy Fabian</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>alfanda.20225001@student.atmi.ac.id</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>pmatmi</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>20225001</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
+      <c r="G25" s="13" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr"/>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Mahasiswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>SHEET2 — Data Perusahaan Magang</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Kolom</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Wajib?</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Nama perusahaan tempat mahasiswa magang. Harus unik, dan penulisannya harus PERSIS SAMA dengan yang akan dipakai di kolom 'nama_perusahaan' pada Sheet3.</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>alamat</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Alamat lengkap perusahaan.</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Contoh pengisian 1 baris data (baris ini hanya contoh, TIDAK ada di Sheet2 yang sebenarnya):</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>alamat</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>PT. Dharma Electrindo Manufactur</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Jl Jababeka XII Blok W no 5A Kawasan Industri Jababeka I Cikarang Utara Bekasi 17530</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>SHEET3 — Penempatan Peserta Magang</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Kolom</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Wajib?</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>nim_mahasiswa</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Harus PERSIS SAMA dengan kolom 'nim' di Sheet1. Kalau tidak cocok, baris ini akan GAGAL diimport.</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>nama_perusahaan</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Wajib</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Harus PERSIS SAMA dengan kolom 'nama' di Sheet2 (termasuk huruf besar/kecil &amp; spasi). Kalau tidak cocok, baris ini akan GAGAL diimport.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>tanggal_presentasi / jam_presentasi / jam_presentasi_selesai / lokasi</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Boleh kosong</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Boleh dikosongkan dulu, bisa diisi/diatur belakangan lewat sistem.</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Contoh pengisian 1 baris data (baris ini hanya contoh, TIDAK ada di Sheet3 yang sebenarnya):</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>nim_mahasiswa</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>nama_perusahaan</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>tanggal_presentasi</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>jam_presentasi</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>jam_presentasi_selesai</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>lokasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>20225001</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>PT. Dharma Electrindo Manufactur</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr"/>
+      <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr"/>
+      <c r="F46" s="13" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>KESALAHAN YANG SERING TERJADI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Baris 'Catatan' atau baris kosong ikut tertinggal di Sheet1/2/3 → upload GAGAL total. Pastikan Sheet1/2/3 hanya berisi baris judul + data asli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Nama perusahaan di Sheet3 ditulis beda (misal beda spasi/singkatan) dari Sheet2 → baris itu GAGAL diimport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>NIM di Sheet3 tidak sama persis dengan NIM di Sheet1 → baris itu GAGAL diimport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Email tidak pakai domain @student.atmi.ac.id → mahasiswa tidak akan bisa login.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:K4"/>
+  <mergeCells count="30">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E78"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="45" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" style="14" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="4"/>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>nim</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>nik</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>nidn</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>gelar_depan</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>gelar_belakang</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>jabatan</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:B4"/>
-  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Role tidak valid" error="Sheet ini khusus data Mahasiswa. Pilih 'Mahasiswa' dari dropdown." type="list">
+      <formula1>"Mahasiswa"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E78"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="22" customWidth="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>alamat</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E78"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="14" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>nim_mahasiswa</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>nama_perusahaan</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>tanggal_presentasi</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>jam_presentasi</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>jam_presentasi_selesai</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>lokasi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>